--- a/docs/oc-regiones/_global/sin-informacion.xlsx
+++ b/docs/oc-regiones/_global/sin-informacion.xlsx
@@ -573,7 +573,11 @@
           <t>88.417.000-1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/_global/sin-informacion.xlsx
+++ b/docs/oc-regiones/_global/sin-informacion.xlsx
@@ -520,42 +520,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pasajes aéreos nacionales</t>
+          <t>Alimentos</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1501163-1-CM26</t>
+          <t>1272238-1-CM26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2239-16-LR23</t>
+          <t>2239-9-LR24</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>65.050.600-6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SKY AIRLINE S A</t>
+          <t>COMERCIAL MAURICIO HERNÁN LÓPEZ CERDA EMPRESA INDIVIDUAL DE RESPONSABILIDAD LIMITADA</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>88.417.000-1</t>
+          <t>78.030.605-K</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="N2" s="2" t="n">
-        <v>335.36</v>
+        <v>3490.99</v>
       </c>
     </row>
   </sheetData>
